--- a/TH1MKT.xlsx
+++ b/TH1MKT.xlsx
@@ -11,141 +11,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="35">
   <si>
     <t/>
   </si>
   <si>
+    <t>10002350</t>
+  </si>
+  <si>
+    <t>ABC KCP MNS B 275 ML</t>
+  </si>
+  <si>
+    <t>TH1MKT</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10003091</t>
+  </si>
+  <si>
+    <t>SOSRO CELUP BLCT30X2</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10022742</t>
+  </si>
+  <si>
+    <t>POCI TEH CLP VNL25X2</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
     <t>20044334</t>
   </si>
   <si>
     <t>SOSRO TEH KTK 300 ML</t>
   </si>
   <si>
-    <t>TH1MKT</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10001365</t>
-  </si>
-  <si>
-    <t>NYAM2 STICK CHOCO 25</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10003404</t>
-  </si>
-  <si>
-    <t>NYAM2 STICK STRAW 25</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10003424</t>
-  </si>
-  <si>
-    <t>NYAM2 B/PUFF CHO 18G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10017675</t>
-  </si>
-  <si>
-    <t>NYAM2 STCK CHOBRY 25</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10036887</t>
-  </si>
-  <si>
-    <t>NYAM2 STK S/CHO 22.5</t>
-  </si>
-  <si>
-    <t>20072581</t>
-  </si>
-  <si>
-    <t>IDM SEAWEED ORG 20G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20072582</t>
-  </si>
-  <si>
-    <t>IDM SEAWEED BBQ 20G</t>
-  </si>
-  <si>
-    <t>10002989</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 135</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20010272</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMB EXT 135</t>
-  </si>
-  <si>
-    <t>20142831</t>
-  </si>
-  <si>
-    <t>LUX BW FREESIA 300G</t>
-  </si>
-  <si>
-    <t>PT,(E-27H)</t>
-  </si>
-  <si>
-    <t>20142832</t>
-  </si>
-  <si>
-    <t>LUX BW SNDL WOOD 300</t>
-  </si>
-  <si>
-    <t>10037405</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 30</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20141440</t>
-  </si>
-  <si>
-    <t>C/L KY PTH CHAMILE60</t>
-  </si>
-  <si>
-    <t>20141441</t>
-  </si>
-  <si>
-    <t>C.LANG BAYI LVD 60 G</t>
-  </si>
-  <si>
-    <t>20140679</t>
-  </si>
-  <si>
-    <t>IDM FC.TISSUE 3X80'S</t>
-  </si>
-  <si>
-    <t>RT</t>
+    <t>20047037</t>
+  </si>
+  <si>
+    <t>IDM KCANG BALI 150 G</t>
+  </si>
+  <si>
+    <t>20093101</t>
+  </si>
+  <si>
+    <t>ZEN BW A.BAC SHIS380</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20108708</t>
+  </si>
+  <si>
+    <t>PEPSODENT COMP8 150G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20120206</t>
+  </si>
+  <si>
+    <t>PPSODENT PG HRBL 150</t>
+  </si>
+  <si>
+    <t>20135211</t>
+  </si>
+  <si>
+    <t>20137884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHUPA JELLY FUN MIX </t>
+  </si>
+  <si>
+    <t>20137885</t>
+  </si>
+  <si>
+    <t>CHUPA JELY OCEAN FUN</t>
   </si>
   <si>
     <t>20138518</t>
@@ -155,21 +116,6 @@
   </si>
   <si>
     <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20108708</t>
-  </si>
-  <si>
-    <t>PEPSODENT COMP8 150G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10037208</t>
-  </si>
-  <si>
-    <t>CLOSE UP MT.FH 100 G</t>
   </si>
 </sst>
 </file>
@@ -562,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -626,10 +572,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -646,59 +592,59 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
@@ -706,50 +652,50 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -763,213 +709,93 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
